--- a/cet4/result/89_律政女神_律师女王的正义/89_律政女神_律师女王的正义_学习版.xlsx
+++ b/cet4/result/89_律政女神_律师女王的正义/89_律政女神_律师女王的正义_学习版.xlsx
@@ -399,416 +399,416 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D29"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>residence</v>
       </c>
       <c r="B2" t="str">
-        <v>residence</v>
+        <v>/ˈrezɪdəns/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>住所</v>
       </c>
-      <c r="D2" t="str">
-        <v>residence(住所)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>salt</v>
       </c>
       <c r="B3" t="str">
-        <v>salt</v>
+        <v>/sɔːlt/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>盐</v>
       </c>
-      <c r="D3" t="str">
-        <v>salt(盐)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>self</v>
       </c>
       <c r="B4" t="str">
-        <v>self</v>
+        <v>/self/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>自己</v>
       </c>
-      <c r="D4" t="str">
-        <v>self(自己)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>layout</v>
       </c>
       <c r="B5" t="str">
-        <v>layout</v>
+        <v>/ˈleɪaʊt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>布局</v>
       </c>
-      <c r="D5" t="str">
-        <v>layout(布局)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>enough</v>
       </c>
       <c r="B6" t="str">
-        <v>enough</v>
+        <v>/ɪˈnʌf/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v./adj./adv./int.</v>
+      </c>
+      <c r="D6" t="str">
         <v>足够</v>
       </c>
-      <c r="D6" t="str">
-        <v>enough(足够)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>advise</v>
       </c>
       <c r="B7" t="str">
-        <v>advise</v>
+        <v>/ədˈvaɪz/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>建议</v>
       </c>
-      <c r="D7" t="str">
-        <v>advise(建议)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>continent</v>
       </c>
       <c r="B8" t="str">
-        <v>continent</v>
+        <v>/ˈkɑːntɪnənt/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>大陆</v>
       </c>
-      <c r="D8" t="str">
-        <v>continent(大陆)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>red</v>
       </c>
       <c r="B9" t="str">
-        <v>red</v>
+        <v>/red/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>红色</v>
       </c>
-      <c r="D9" t="str">
-        <v>red(红色)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>bank</v>
       </c>
       <c r="B10" t="str">
-        <v>bank</v>
+        <v>/bæŋk/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>银行</v>
       </c>
-      <c r="D10" t="str">
-        <v>bank(银行)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>succeed</v>
       </c>
       <c r="B11" t="str">
-        <v>succeed</v>
+        <v>/səkˈsiːd/</v>
       </c>
       <c r="C11" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>成功</v>
       </c>
-      <c r="D11" t="str">
-        <v>succeed(成功)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>target</v>
       </c>
       <c r="B12" t="str">
-        <v>target</v>
+        <v>/ˈtɑːrɡɪt/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D12" t="str">
         <v>目标</v>
       </c>
-      <c r="D12" t="str">
-        <v>target(目标)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>accordance</v>
       </c>
       <c r="B13" t="str">
-        <v>accordance</v>
+        <v>/əˈkɔːrdns/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>按照</v>
       </c>
-      <c r="D13" t="str">
-        <v>accordance(按照)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>keep</v>
       </c>
       <c r="B14" t="str">
-        <v>keep</v>
+        <v>/kiːp/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>保持</v>
       </c>
-      <c r="D14" t="str">
-        <v>keep(保持)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>robber</v>
       </c>
       <c r="B15" t="str">
-        <v>robber</v>
+        <v>/ˈrɑːbər/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>强盗</v>
       </c>
-      <c r="D15" t="str">
-        <v>robber(强盗)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>pocket</v>
       </c>
       <c r="B16" t="str">
-        <v>pocket</v>
+        <v>/ˈpɑːkɪt/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>口袋</v>
       </c>
-      <c r="D16" t="str">
-        <v>pocket(口袋)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>goods</v>
       </c>
       <c r="B17" t="str">
-        <v>goods</v>
+        <v>/ɡʊdz/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>商品</v>
       </c>
-      <c r="D17" t="str">
-        <v>goods(商品)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>capable</v>
       </c>
       <c r="B18" t="str">
-        <v>capable</v>
+        <v>/ˈkeɪpəbl/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>有能力的</v>
       </c>
-      <c r="D18" t="str">
-        <v>capable(有能力的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>never</v>
       </c>
       <c r="B19" t="str">
-        <v>never</v>
+        <v>/ˈnevər/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D19" t="str">
         <v>从未</v>
       </c>
-      <c r="D19" t="str">
-        <v>never(从未)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>staircase</v>
       </c>
       <c r="B20" t="str">
-        <v>staircase</v>
+        <v>/ˈsterkeɪs/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>楼梯</v>
       </c>
-      <c r="D20" t="str">
-        <v>staircase(楼梯)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>admit</v>
       </c>
       <c r="B21" t="str">
-        <v>admit</v>
+        <v>/ədˈmɪt/</v>
       </c>
       <c r="C21" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>承认</v>
       </c>
-      <c r="D21" t="str">
-        <v>admit(承认)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>flesh</v>
       </c>
       <c r="B22" t="str">
-        <v>flesh</v>
+        <v>/fleʃ/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>血肉</v>
       </c>
-      <c r="D22" t="str">
-        <v>flesh(血肉)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>season</v>
       </c>
       <c r="B23" t="str">
-        <v>season</v>
+        <v>/ˈsiːzn/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>季节</v>
       </c>
-      <c r="D23" t="str">
-        <v>season(季节)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>best</v>
       </c>
       <c r="B24" t="str">
-        <v>best</v>
+        <v>/best/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>最好的</v>
       </c>
-      <c r="D24" t="str">
-        <v>best(最好的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>gaze</v>
       </c>
       <c r="B25" t="str">
-        <v>gaze</v>
+        <v>/ɡeɪz/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D25" t="str">
         <v>凝视</v>
       </c>
-      <c r="D25" t="str">
-        <v>gaze(凝视)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>register</v>
       </c>
       <c r="B26" t="str">
-        <v>register</v>
+        <v>/ˈredʒɪstər/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D26" t="str">
         <v>登记</v>
       </c>
-      <c r="D26" t="str">
-        <v>register(登记)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>wonder</v>
       </c>
       <c r="B27" t="str">
-        <v>wonder</v>
+        <v>/ˈwʌndər/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>奇迹</v>
       </c>
-      <c r="D27" t="str">
-        <v>wonder(奇迹)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>consumption</v>
       </c>
       <c r="B28" t="str">
-        <v>consumption</v>
+        <v>/kənˈsʌmpʃn/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>消费</v>
       </c>
-      <c r="D28" t="str">
-        <v>consumption(消费)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>thermometer</v>
       </c>
       <c r="B29" t="str">
-        <v>thermometer</v>
+        <v>/θərˈmɑːmɪtər/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>温度计</v>
-      </c>
-      <c r="D29" t="str">
-        <v>thermometer(温度计)📢</v>
       </c>
     </row>
   </sheetData>
